--- a/DesignData/EnemyConfig.xlsx
+++ b/DesignData/EnemyConfig.xlsx
@@ -1,260 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20415" windowHeight="12705"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24885" windowHeight="12705" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyConfig" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
-  <si>
-    <t>EnemyType</t>
-  </si>
-  <si>
-    <t>enemySize</t>
-  </si>
-  <si>
-    <t>MaxHealth</t>
-  </si>
-  <si>
-    <t>ReactionTime</t>
-  </si>
-  <si>
-    <t>Speed</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>DetectionRange</t>
-  </si>
-  <si>
-    <t>AttackMaxRange</t>
-  </si>
-  <si>
-    <t>AttackMinRange</t>
-  </si>
-  <si>
-    <t>MoveSpeed</t>
-  </si>
-  <si>
-    <t>KnockbackThreshold</t>
-  </si>
-  <si>
-    <t>BurnThreshold</t>
-  </si>
-  <si>
-    <t>SlowThreshold</t>
-  </si>
-  <si>
-    <t>enum:EnemyTypeEnum</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>Worker</t>
-  </si>
-  <si>
-    <t>Warrior_AR</t>
-  </si>
-  <si>
-    <t>Raider</t>
-  </si>
-  <si>
-    <t>Dropper_Mid</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -554,158 +471,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -951,7 +869,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -960,7 +878,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -973,11 +891,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1237,271 +1218,451 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="19.25" customWidth="1"/>
-    <col min="2" max="2" width="13.5" customWidth="1"/>
-    <col min="3" max="3" width="13.125" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="7" max="7" width="16.625" customWidth="1"/>
-    <col min="8" max="8" width="14.75" customWidth="1"/>
-    <col min="9" max="9" width="16.375" customWidth="1"/>
-    <col min="10" max="10" width="14.625" customWidth="1"/>
-    <col min="11" max="11" width="19.75" customWidth="1"/>
-    <col min="12" max="13" width="18.125" customWidth="1"/>
+    <col width="19.25" customWidth="1" style="1" min="1" max="1"/>
+    <col width="13.5" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13.125" customWidth="1" style="1" min="3" max="3"/>
+    <col width="13" customWidth="1" style="1" min="4" max="4"/>
+    <col width="16.625" customWidth="1" style="1" min="7" max="7"/>
+    <col width="14.75" customWidth="1" style="1" min="8" max="8"/>
+    <col width="16.375" customWidth="1" style="1" min="9" max="9"/>
+    <col width="14.625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="19.75" customWidth="1" style="1" min="11" max="11"/>
+    <col width="18.125" customWidth="1" style="1" min="12" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>EnemyType</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>enemySize</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>MaxHealth</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>ReactionTime</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>DetectionRange</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>AttackMaxRange</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>AttackMinRange</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>StopRange</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>ShootAccuracy</t>
+        </is>
+      </c>
+      <c r="L1" s="0" t="inlineStr">
+        <is>
+          <t>BulletSpeed</t>
+        </is>
+      </c>
+      <c r="M1" s="0" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <is>
+          <t>KnockbackThreshold</t>
+        </is>
+      </c>
+      <c r="O1" s="0" t="inlineStr">
+        <is>
+          <t>BurnThreshold</t>
+        </is>
+      </c>
+      <c r="P1" s="0" t="inlineStr">
+        <is>
+          <t>SlowThreshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>enum:EnemyTypeEnum</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Worker</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="J3" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>Warrior_AR</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="N4" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Warrior_SN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>Raider</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="K6" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="N6" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O6" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P6" s="0" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>Dropper_Mid</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="I7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>0.5</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>15</v>
-      </c>
-      <c r="H3">
-        <v>2.5</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
+      <c r="M7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K3">
-        <v>0.5</v>
-      </c>
-      <c r="L3">
-        <v>0.6</v>
-      </c>
-      <c r="M3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4">
-        <v>0.5</v>
-      </c>
-      <c r="E4">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
-      </c>
-      <c r="G4">
-        <v>15</v>
-      </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>0.3</v>
-      </c>
-      <c r="L4">
-        <v>0.4</v>
-      </c>
-      <c r="M4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>0.5</v>
-      </c>
-      <c r="E5">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>30</v>
-      </c>
-      <c r="G5">
-        <v>20</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>0.25</v>
-      </c>
-      <c r="L5">
-        <v>0.3</v>
-      </c>
-      <c r="M5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>30</v>
-      </c>
-      <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
+      <c r="N7" s="0" t="n">
         <v>999</v>
       </c>
-      <c r="L6">
+      <c r="O7" s="0" t="n">
         <v>999</v>
       </c>
-      <c r="M6">
+      <c r="P7" s="0" t="n">
         <v>999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/DesignData/EnemyConfig.xlsx
+++ b/DesignData/EnemyConfig.xlsx
@@ -1,177 +1,272 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24885" windowHeight="12705" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="24885" windowHeight="12705"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyConfig" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EnemyConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+  <si>
+    <t>EnemyType</t>
+  </si>
+  <si>
+    <t>enemySize</t>
+  </si>
+  <si>
+    <t>MaxHealth</t>
+  </si>
+  <si>
+    <t>ReactionTime</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>DetectionRange</t>
+  </si>
+  <si>
+    <t>AttackMaxRange</t>
+  </si>
+  <si>
+    <t>AttackMinRange</t>
+  </si>
+  <si>
+    <t>StopRange</t>
+  </si>
+  <si>
+    <t>ShootAccuracy</t>
+  </si>
+  <si>
+    <t>BulletSpeed</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
+    <t>KnockbackThreshold</t>
+  </si>
+  <si>
+    <t>BurnThreshold</t>
+  </si>
+  <si>
+    <t>SlowThreshold</t>
+  </si>
+  <si>
+    <t>enum:EnemyTypeEnum</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>Worker</t>
+  </si>
+  <si>
+    <t>Warrior_AR</t>
+  </si>
+  <si>
+    <t>Warrior_SN</t>
+  </si>
+  <si>
+    <t>Raider</t>
+  </si>
+  <si>
+    <t>Dropper_Mid</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -471,159 +566,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -869,7 +964,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -878,7 +973,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -891,74 +986,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1218,451 +1250,375 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:P7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col width="19.25" customWidth="1" style="1" min="1" max="1"/>
-    <col width="13.5" customWidth="1" style="1" min="2" max="2"/>
-    <col width="13.125" customWidth="1" style="1" min="3" max="3"/>
-    <col width="13" customWidth="1" style="1" min="4" max="4"/>
-    <col width="16.625" customWidth="1" style="1" min="7" max="7"/>
-    <col width="14.75" customWidth="1" style="1" min="8" max="8"/>
-    <col width="16.375" customWidth="1" style="1" min="9" max="9"/>
-    <col width="14.625" customWidth="1" style="1" min="10" max="10"/>
-    <col width="19.75" customWidth="1" style="1" min="11" max="11"/>
-    <col width="18.125" customWidth="1" style="1" min="12" max="13"/>
+    <col min="1" max="1" width="19.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.75" style="1" customWidth="1"/>
+    <col min="12" max="13" width="18.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>EnemyType</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>enemySize</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>MaxHealth</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>ReactionTime</t>
-        </is>
-      </c>
-      <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="F1" s="0" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>DetectionRange</t>
-        </is>
-      </c>
-      <c r="H1" s="0" t="inlineStr">
-        <is>
-          <t>AttackMaxRange</t>
-        </is>
-      </c>
-      <c r="I1" s="0" t="inlineStr">
-        <is>
-          <t>AttackMinRange</t>
-        </is>
-      </c>
-      <c r="J1" s="0" t="inlineStr">
-        <is>
-          <t>StopRange</t>
-        </is>
-      </c>
-      <c r="K1" s="0" t="inlineStr">
-        <is>
-          <t>ShootAccuracy</t>
-        </is>
-      </c>
-      <c r="L1" s="0" t="inlineStr">
-        <is>
-          <t>BulletSpeed</t>
-        </is>
-      </c>
-      <c r="M1" s="0" t="inlineStr">
-        <is>
-          <t>MoveSpeed</t>
-        </is>
-      </c>
-      <c r="N1" s="0" t="inlineStr">
-        <is>
-          <t>KnockbackThreshold</t>
-        </is>
-      </c>
-      <c r="O1" s="0" t="inlineStr">
-        <is>
-          <t>BurnThreshold</t>
-        </is>
-      </c>
-      <c r="P1" s="0" t="inlineStr">
-        <is>
-          <t>SlowThreshold</t>
-        </is>
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>enum:EnemyTypeEnum</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="I2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="O2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>Worker</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="n">
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3">
         <v>50</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3">
         <v>0.5</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3">
         <v>10</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3">
         <v>5</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3">
         <v>15</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3">
         <v>2.5</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3">
         <v>1.5</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3">
         <v>1</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3">
         <v>20</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3">
         <v>3</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3">
         <v>0.5</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3">
         <v>0.6</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="P3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>Warrior_AR</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="n">
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
         <v>10</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4">
         <v>100</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4">
         <v>0.5</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4">
         <v>20</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4">
         <v>20</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4">
         <v>15</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4">
         <v>12</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4">
         <v>8</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4">
         <v>5</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4">
         <v>0.5</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4">
         <v>10</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4">
         <v>2</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4">
         <v>0.3</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4">
         <v>0.4</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Warrior_SN</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5">
         <v>10</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>80</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>20</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>50</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>20</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>18</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>25</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="L5">
+        <v>45</v>
+      </c>
+      <c r="M5">
         <v>1.5</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>0.3</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>0.3</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>Raider</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="n">
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6">
         <v>15</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6">
         <v>50</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6">
         <v>0.5</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6">
         <v>30</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6">
         <v>30</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6">
         <v>20</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6">
         <v>8</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6">
         <v>3</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6">
         <v>0.5</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6">
         <v>10</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6">
         <v>4</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6">
         <v>0.25</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6">
         <v>0.3</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6">
         <v>0.5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>Dropper_Mid</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="n">
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
         <v>15</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7">
         <v>10</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7">
         <v>30</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7">
         <v>30</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7">
         <v>20</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7">
         <v>5</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7">
         <v>1.5</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7">
         <v>3</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7">
         <v>999</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7">
         <v>999</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7">
         <v>999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/DesignData/EnemyConfig.xlsx
+++ b/DesignData/EnemyConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>EnemyType</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>SlowThreshold</t>
+  </si>
+  <si>
+    <t>AttackCooldown</t>
   </si>
   <si>
     <t>enum:EnemyTypeEnum</t>
@@ -1252,7 +1255,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="19.25" style="1" customWidth="1"/>
@@ -1265,9 +1268,10 @@
     <col min="10" max="10" width="14.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="19.75" style="1" customWidth="1"/>
     <col min="12" max="13" width="18.125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1316,60 +1320,66 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -1416,10 +1426,13 @@
       <c r="P3">
         <v>0.5</v>
       </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -1466,10 +1479,13 @@
       <c r="P4">
         <v>0.5</v>
       </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1496,13 +1512,13 @@
         <v>12</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M5">
         <v>1.5</v>
@@ -1516,10 +1532,13 @@
       <c r="P5">
         <v>0.5</v>
       </c>
+      <c r="Q5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>15</v>
@@ -1566,16 +1585,19 @@
       <c r="P6">
         <v>0.5</v>
       </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>15</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1615,6 +1637,9 @@
       </c>
       <c r="P7">
         <v>999</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
